--- a/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2003_2014/tabelas/testes_estacionariedade.xlsx
+++ b/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2003_2014/tabelas/testes_estacionariedade.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IPCA_Geral_nivel</t>
+          <t>Preco_Barril</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.386521686716927</v>
+        <v>-2.243041044237509</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9990038249169402</v>
+        <v>0.1909963717017669</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="H2" t="n">
-        <v>1.681735621268447</v>
+        <v>1.298594273981718</v>
       </c>
       <c r="I2" t="n">
         <v>0.01</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IPCA_Geral_nivel</t>
+          <t>Preco_Barril</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-3.442079034586364</v>
+        <v>-5.373520988496589</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009605355906026857</v>
+        <v>3.849071562463055e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1383793113378584</v>
+        <v>0.1658762618405615</v>
       </c>
       <c r="I3" t="n">
         <v>0.1</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IPCA_Trans_nivel</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.751255608545256</v>
+        <v>-3.313645663423265</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4049160913998124</v>
+        <v>0.01427942307469208</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H4" t="n">
-        <v>1.626697397914636</v>
+        <v>0.8526236628220215</v>
       </c>
       <c r="I4" t="n">
         <v>0.01</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IPCA_Trans_nivel</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -613,25 +613,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-2.447442414552239</v>
+        <v>-7.69834433892167</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1287912206108532</v>
+        <v>1.360218806182835e-11</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2683356839852704</v>
+        <v>0.4562057538662571</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1</v>
+        <v>0.05292855436799266</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>143</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Atividade</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-3.313645663423265</v>
+        <v>-1.073548545127125</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01427942307469208</v>
+        <v>0.7255043640378228</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -994,7 +994,7 @@
         <v>142</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8526236628220215</v>
+        <v>1.656474521283946</v>
       </c>
       <c r="I14" t="n">
         <v>0.01</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Atividade</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1023,25 +1023,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-7.69834433892167</v>
+        <v>-6.752645169894729</v>
       </c>
       <c r="E15" t="n">
-        <v>1.360218806182835e-11</v>
+        <v>2.924582407414671e-09</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4562057538662571</v>
+        <v>0.1968193563619644</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05292855436799266</v>
+        <v>0.1</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
         <v>143</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Preco_Barril</t>
+          <t>Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1064,22 +1064,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-2.243041044237509</v>
+        <v>-2.588567418543708</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1909963717017669</v>
+        <v>0.09538324615389943</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H16" t="n">
-        <v>1.298594273981718</v>
+        <v>0.339199814148152</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="J16" t="n">
         <v>8</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Preco_Barril</t>
+          <t>Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1105,25 +1105,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-5.373520988496589</v>
+        <v>-4.959919969010081</v>
       </c>
       <c r="E17" t="n">
-        <v>3.849071562463055e-06</v>
+        <v>2.662454654671287e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1658762618405615</v>
+        <v>0.7211714443055209</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1</v>
+        <v>0.01162077779040719</v>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
         <v>143</v>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Atividade</t>
+          <t>Selic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-1.073548545127125</v>
+        <v>-1.415459308216703</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7255043640378228</v>
+        <v>0.5748427036212234</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G18" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="H18" t="n">
-        <v>1.656474521283946</v>
+        <v>1.292893293280039</v>
       </c>
       <c r="I18" t="n">
         <v>0.01</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Atividade</t>
+          <t>Selic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1187,25 +1187,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-6.752645169894729</v>
+        <v>-3.604151248479291</v>
       </c>
       <c r="E19" t="n">
-        <v>2.924582407414671e-09</v>
+        <v>0.005682158933290642</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G19" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1968193563619644</v>
+        <v>0.1819964891215249</v>
       </c>
       <c r="I19" t="n">
         <v>0.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K19" t="n">
         <v>143</v>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Selic</t>
+          <t>IPCA_Trans_nivel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1228,19 +1228,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.415459308216703</v>
+        <v>-1.751255608545256</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5748427036212234</v>
+        <v>0.4049160913998124</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H20" t="n">
-        <v>1.292893293280039</v>
+        <v>1.626697397914636</v>
       </c>
       <c r="I20" t="n">
         <v>0.01</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Selic</t>
+          <t>IPCA_Trans_nivel</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1269,25 +1269,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-3.604151248479291</v>
+        <v>-2.447442414552239</v>
       </c>
       <c r="E21" t="n">
-        <v>0.005682158933290642</v>
+        <v>0.1287912206108532</v>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1819964891215249</v>
+        <v>0.2683356839852704</v>
       </c>
       <c r="I21" t="n">
         <v>0.1</v>
       </c>
       <c r="J21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
         <v>143</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Expectativa_Inflacao</t>
+          <t>IPCA_Geral_nivel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1310,22 +1310,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-2.588567418543708</v>
+        <v>2.386521686716927</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09538324615389943</v>
+        <v>0.9990038249169402</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H22" t="n">
-        <v>0.339199814148152</v>
+        <v>1.681735621268447</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="J22" t="n">
         <v>8</v>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Expectativa_Inflacao</t>
+          <t>IPCA_Geral_nivel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1351,25 +1351,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-4.959919969010081</v>
+        <v>-3.442079034586364</v>
       </c>
       <c r="E23" t="n">
-        <v>2.662454654671287e-05</v>
+        <v>0.009605355906026857</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7211714443055209</v>
+        <v>0.1383793113378584</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01162077779040719</v>
+        <v>0.1</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K23" t="n">
         <v>143</v>
